--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56107D6-46CF-46CD-A74D-D0C2BB2EAFED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C9B619-9D4F-4EE8-BBDB-0FB96BE57A96}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B041ACD-DF6A-4BD4-8AE6-506A95369509}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5814FB20-4C01-4FD1-81C2-A9642273EF04}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="35">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -62,18 +62,9 @@
     <t>Overview</t>
   </si>
   <si>
-    <t>Abbreviation__c</t>
-  </si>
-  <si>
-    <t>WebsiteAddress__c</t>
-  </si>
-  <si>
     <t>http://automate.com</t>
   </si>
   <si>
-    <t>Objectives__c</t>
-  </si>
-  <si>
     <t>RichText</t>
   </si>
   <si>
@@ -92,12 +83,6 @@
     <t>IsGoalsRequired__c</t>
   </si>
   <si>
-    <t>Test Automation Organization</t>
-  </si>
-  <si>
-    <t>ProgramName__c</t>
-  </si>
-  <si>
     <t>PREG</t>
   </si>
   <si>
@@ -114,13 +99,43 @@
   </si>
   <si>
     <t>Automation Runtime Execution Internal Program in another ORG</t>
+  </si>
+  <si>
+    <t>fieldProgramName__c</t>
+  </si>
+  <si>
+    <t>fieldType__c</t>
+  </si>
+  <si>
+    <t>fieldPrimaryFundingOrganization__c</t>
+  </si>
+  <si>
+    <t>Automation Internal Org</t>
+  </si>
+  <si>
+    <t>fieldFocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>fieldIsGoalsRequired__c</t>
+  </si>
+  <si>
+    <t>fieldKPIsRequired__c</t>
+  </si>
+  <si>
+    <t>fieldAbbreviation__c</t>
+  </si>
+  <si>
+    <t>fieldWebsiteAddress__c</t>
+  </si>
+  <si>
+    <t>fieldObjectives__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,6 +150,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -158,7 +179,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -167,6 +188,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -449,14 +471,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -467,70 +489,70 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>18</v>
+      <c r="B5" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -545,13 +567,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.9296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,18 +584,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -584,7 +606,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -592,48 +614,48 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -645,14 +667,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -663,37 +685,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
       <c r="C3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -704,13 +726,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -718,7 +740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -726,7 +748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -734,25 +756,25 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -765,13 +787,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -782,37 +804,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
-        <v>12</v>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>15</v>
+      <c r="B4" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD10F27-EC68-4ED0-B54C-4EFBE52702AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405E481F-B2D4-46A5-96A9-6AA3F488F3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="33">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -51,57 +51,30 @@
     <t>Dropdown</t>
   </si>
   <si>
-    <t>Type__c</t>
-  </si>
-  <si>
     <t>Project Grants</t>
   </si>
   <si>
     <t>Lookup</t>
   </si>
   <si>
-    <t>PrimaryFundingOrganization__c</t>
-  </si>
-  <si>
     <t>Overview</t>
   </si>
   <si>
-    <t>Abbreviation__c</t>
-  </si>
-  <si>
-    <t>WebsiteAddress__c</t>
-  </si>
-  <si>
     <t>http://automate.com</t>
   </si>
   <si>
-    <t>Objectives__c</t>
-  </si>
-  <si>
     <t>RichText</t>
   </si>
   <si>
     <t>Automation test description</t>
   </si>
   <si>
-    <t>FocusAreaRequired__c</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>KPIsRequired__c</t>
-  </si>
-  <si>
-    <t>IsGoalsRequired__c</t>
-  </si>
-  <si>
     <t>Test Automation Organization</t>
   </si>
   <si>
-    <t>ProgramName__c</t>
-  </si>
-  <si>
     <t>PREG</t>
   </si>
   <si>
@@ -133,6 +106,27 @@
   </si>
   <si>
     <t>Automation Runtime Internal Program For Bulk Records</t>
+  </si>
+  <si>
+    <t>fieldProgramName__c</t>
+  </si>
+  <si>
+    <t>fieldType__c</t>
+  </si>
+  <si>
+    <t>fieldWebsiteAddress__c</t>
+  </si>
+  <si>
+    <t>fieldPrimaryFundingOrganization__c</t>
+  </si>
+  <si>
+    <t>fieldFocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>fieldIsGoalsRequired__c</t>
+  </si>
+  <si>
+    <t>fieldKPIsRequired__c</t>
   </si>
 </sst>
 </file>
@@ -468,13 +462,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,70 +479,70 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
+      <c r="B2" t="s">
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -562,14 +556,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -580,70 +574,70 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
+      <c r="B2" t="s">
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -658,13 +652,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -675,70 +669,70 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
+      <c r="B2" t="s">
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -752,13 +746,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -769,78 +763,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
+      <c r="B2" t="s">
+        <v>26</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -852,14 +846,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -870,37 +864,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -911,13 +905,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -925,7 +919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -933,7 +927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -941,25 +935,25 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -972,13 +966,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -989,37 +983,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1034,14 +1028,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1052,48 +1046,48 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
         <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1104,14 +1098,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1122,15 +1116,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD10F27-EC68-4ED0-B54C-4EFBE52702AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4E788B-5367-4EBB-8A68-E12AF720F713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -120,19 +120,16 @@
     <t>Automation Runtime Execution Internal Program in another ORG</t>
   </si>
   <si>
-    <t>fieldAbbreviation__c</t>
-  </si>
-  <si>
     <t>Automation Program</t>
   </si>
   <si>
     <t>Test With Automation PM</t>
   </si>
   <si>
-    <t>fieldObjectives__c</t>
-  </si>
-  <si>
     <t>Automation Runtime Internal Program For Bulk Records</t>
+  </si>
+  <si>
+    <t>Account__c</t>
   </si>
 </sst>
 </file>
@@ -468,13 +465,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,7 +482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -493,10 +490,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -507,7 +504,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -518,7 +515,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -529,7 +526,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -540,7 +537,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -562,14 +559,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -580,7 +577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -591,7 +588,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -602,7 +599,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -613,7 +610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -624,7 +621,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -635,7 +632,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -658,13 +655,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -686,7 +683,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -697,7 +694,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -708,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -719,7 +716,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -730,7 +727,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -752,13 +749,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -769,7 +766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -780,7 +777,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -791,7 +788,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -802,7 +799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -813,7 +810,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -824,7 +821,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -835,7 +832,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -852,14 +849,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -870,7 +867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -881,7 +878,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -892,7 +889,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -911,13 +908,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -925,7 +922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -933,7 +930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -941,7 +938,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -949,17 +946,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -972,13 +969,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -989,7 +986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1000,7 +997,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1011,7 +1008,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1034,14 +1031,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1063,7 +1060,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1074,26 +1071,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
         <v>30</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1104,14 +1101,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1122,12 +1119,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4E788B-5367-4EBB-8A68-E12AF720F713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7772E65D-8129-4975-83A5-2F36BDF125D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7772E65D-8129-4975-83A5-2F36BDF125D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4541981-D1C6-446F-AD9D-936A0F9675FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -120,9 +120,6 @@
     <t>Automation Runtime Execution Internal Program in another ORG</t>
   </si>
   <si>
-    <t>Automation Program</t>
-  </si>
-  <si>
     <t>Test With Automation PM</t>
   </si>
   <si>
@@ -130,6 +127,9 @@
   </si>
   <si>
     <t>Account__c</t>
+  </si>
+  <si>
+    <t>Auto</t>
   </si>
 </sst>
 </file>
@@ -465,13 +465,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,7 +482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -490,10 +490,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -504,7 +504,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -515,7 +515,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -526,7 +526,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -537,7 +537,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -559,14 +559,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,7 +577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -588,7 +588,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -599,7 +599,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -610,7 +610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -621,7 +621,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -632,7 +632,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -655,13 +655,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -672,7 +672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -683,7 +683,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -694,7 +694,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -716,7 +716,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -727,7 +727,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -749,13 +749,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -766,7 +766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -777,7 +777,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -788,7 +788,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -799,7 +799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -810,7 +810,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -821,7 +821,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -832,7 +832,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -849,14 +849,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -867,7 +867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -878,7 +878,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -889,7 +889,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -908,13 +908,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -930,7 +930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -938,7 +938,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -946,17 +946,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -969,13 +969,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -986,7 +986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -997,7 +997,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1031,14 +1031,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1079,18 +1079,18 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1101,14 +1101,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4541981-D1C6-446F-AD9D-936A0F9675FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C234CF-A2F8-4FDE-8FC0-BCE8834036A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -136,7 +136,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +151,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -174,7 +180,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -183,6 +189,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -465,13 +472,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,7 +489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -493,7 +500,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -504,7 +511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -515,7 +522,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -526,7 +533,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -537,7 +544,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -559,14 +566,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,7 +584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -588,7 +595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -599,7 +606,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -610,7 +617,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -621,7 +628,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -632,7 +639,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -655,13 +662,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -672,7 +679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -683,7 +690,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -694,7 +701,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -705,7 +712,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -716,7 +723,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -727,7 +734,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -749,13 +756,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -766,7 +773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -777,7 +784,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -788,7 +795,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -799,7 +806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -810,7 +817,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -821,7 +828,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -832,7 +839,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -849,14 +856,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -867,7 +874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -878,7 +885,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -889,7 +896,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -908,13 +915,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -922,7 +929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -930,7 +937,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -938,7 +945,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -946,17 +953,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -969,13 +976,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -986,7 +993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -997,7 +1004,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1008,7 +1015,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1030,15 +1037,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1049,7 +1056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1060,7 +1067,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1071,7 +1078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1082,7 +1089,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1093,22 +1100,26 @@
         <v>30</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1119,7 +1130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C234CF-A2F8-4FDE-8FC0-BCE8834036A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDBB52A-07B4-4CD4-B2BE-9D76ECEBFC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,10 +18,21 @@
     <sheet name="NGOCreation" sheetId="8" r:id="rId8"/>
     <sheet name="NGOEdit" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="179017"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD10F27-EC68-4ED0-B54C-4EFBE52702AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8ACC94E-FA01-47CE-8BFB-D06D37E8090A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="36">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>Automation Runtime Internal Program For Bulk Records</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
   </si>
 </sst>
 </file>
@@ -468,13 +471,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,7 +488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -496,7 +499,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -507,7 +510,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -518,7 +521,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -529,7 +532,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -540,7 +543,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -562,14 +565,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -580,7 +583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -591,7 +594,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -602,7 +605,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -610,10 +613,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -624,7 +627,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -635,7 +638,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -648,7 +651,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{7EE9E90B-967F-44F2-8381-163CD7361D89}"/>
+    <hyperlink ref="C4" r:id="rId1" display="https://test8-internal--508org.sandbox.my.salesforce.com/00E4T000000kkag" xr:uid="{570DBC5A-D8D4-48F6-AB8D-38AB03531C2A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -658,13 +661,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -686,7 +689,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -697,7 +700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -708,7 +711,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -719,7 +722,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -730,7 +733,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -752,13 +755,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -769,7 +772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -780,7 +783,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -791,7 +794,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -802,7 +805,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -813,7 +816,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -824,7 +827,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -835,7 +838,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -852,14 +855,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -870,7 +873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -881,7 +884,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -892,7 +895,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -911,13 +914,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -925,7 +928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -933,7 +936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -941,7 +944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -949,17 +952,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -972,13 +975,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -989,7 +992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1000,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1011,7 +1014,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1034,14 +1037,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1063,7 +1066,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1074,7 +1077,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1085,7 +1088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1104,14 +1107,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1122,7 +1125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8ACC94E-FA01-47CE-8BFB-D06D37E8090A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5D455A-B40C-41D3-AB99-C95F111015D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="35">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -133,9 +133,6 @@
   </si>
   <si>
     <t>Automation Runtime Internal Program For Bulk Records</t>
-  </si>
-  <si>
-    <t>SYSTEM</t>
   </si>
 </sst>
 </file>
@@ -613,7 +610,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -651,7 +648,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" display="https://test8-internal--508org.sandbox.my.salesforce.com/00E4T000000kkag" xr:uid="{570DBC5A-D8D4-48F6-AB8D-38AB03531C2A}"/>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{1A1A9F46-186A-4E2D-A5C6-06089B080175}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5D455A-B40C-41D3-AB99-C95F111015D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2A58ED-F760-431F-A3F4-A4094041F879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="36">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -133,13 +133,16 @@
   </si>
   <si>
     <t>Automation Runtime Internal Program For Bulk Records</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +154,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -177,7 +187,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -186,6 +196,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -609,8 +620,8 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
+      <c r="C4" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -647,11 +658,8 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{1A1A9F46-186A-4E2D-A5C6-06089B080175}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD10F27-EC68-4ED0-B54C-4EFBE52702AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="NGOCreation" sheetId="8" r:id="rId8"/>
     <sheet name="NGOEdit" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="179017"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="41">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -133,13 +132,31 @@
   </si>
   <si>
     <t>Automation Runtime Internal Program For Bulk Records</t>
+  </si>
+  <si>
+    <t>Department of Education</t>
+  </si>
+  <si>
+    <t>North Dakota Industrial Commission</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>Department of Objectives</t>
+  </si>
+  <si>
+    <t>fieldAuthorizedSignatory__c</t>
+  </si>
+  <si>
+    <t>John Rambo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +171,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -177,7 +200,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -186,6 +209,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -466,7 +490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -553,15 +577,15 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{E44E2E55-A2EC-4DFF-AAA5-2623A48FE502}"/>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
@@ -588,18 +612,18 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
+      <c r="B3" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -607,10 +631,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -618,10 +642,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -629,7 +653,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -640,23 +664,31 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{7EE9E90B-967F-44F2-8381-163CD7361D89}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -743,14 +775,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{832EB4E6-689C-4A9F-9F20-5BF3E0292CEF}"/>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -850,7 +882,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -909,7 +941,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -970,11 +1002,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1019,12 +1051,23 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{2964AC08-382B-4FAE-8F45-970C952B4A4E}"/>
+    <hyperlink ref="C3" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
@@ -1032,7 +1075,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1102,7 +1145,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E58013E-34E6-44FD-97DE-79C6228C0DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" activeTab="6"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -155,7 +156,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -490,15 +491,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,7 +510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -520,7 +521,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -531,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -542,7 +543,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -553,7 +554,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -564,7 +565,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -577,23 +578,23 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y"/>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -604,7 +605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -615,7 +616,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -626,7 +627,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -637,7 +638,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -648,7 +649,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -659,7 +660,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -670,7 +671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -688,15 +689,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -707,7 +708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -718,7 +719,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -729,7 +730,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -740,7 +741,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -751,7 +752,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -762,7 +763,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -775,22 +776,22 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y"/>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -801,7 +802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -812,7 +813,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -823,7 +824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -834,7 +835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -845,7 +846,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -856,7 +857,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -867,7 +868,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -882,16 +883,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -902,7 +903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -913,7 +914,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -924,7 +925,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -941,15 +942,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -957,7 +958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -965,7 +966,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -973,7 +974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -981,17 +982,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1002,15 +1003,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1021,7 +1022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1032,7 +1033,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1043,7 +1044,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1054,7 +1055,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1067,7 +1068,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
@@ -1075,16 +1076,16 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1095,7 +1096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1106,7 +1107,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1117,7 +1118,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1128,7 +1129,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1145,16 +1146,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1165,7 +1166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDBB52A-07B4-4CD4-B2BE-9D76ECEBFC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D65893-05AB-41F6-9884-C35C033D4CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="39">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -141,13 +141,28 @@
   </si>
   <si>
     <t>Auto</t>
+  </si>
+  <si>
+    <t>Department of Education</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>Department of Objectives</t>
+  </si>
+  <si>
+    <t>AuthorizedSignatory__c</t>
+  </si>
+  <si>
+    <t>Automation EXE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +180,12 @@
     </font>
     <font>
       <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF1F1F1F"/>
       <name val="Consolas"/>
       <family val="3"/>
@@ -191,7 +212,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -201,6 +222,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -483,13 +505,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,7 +522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -511,7 +533,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -522,7 +544,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -533,7 +555,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -544,7 +566,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -555,7 +577,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -576,15 +598,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -595,7 +617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -603,67 +625,78 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{7EE9E90B-967F-44F2-8381-163CD7361D89}"/>
+    <hyperlink ref="C5" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{C9D0EB6C-C076-4206-9ED1-EEF6171A1B00}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -673,13 +706,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,7 +723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -701,7 +734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -712,7 +745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -723,7 +756,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -734,7 +767,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -745,7 +778,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -767,13 +800,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -784,7 +817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -795,7 +828,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -806,7 +839,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -817,7 +850,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -828,7 +861,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -839,7 +872,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -850,7 +883,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -867,14 +900,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -885,7 +918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -896,7 +929,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -907,7 +940,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -926,13 +959,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -940,7 +973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -948,7 +981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -956,7 +989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -964,17 +997,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -986,14 +1019,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1004,7 +1037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1015,7 +1048,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1026,7 +1059,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1034,12 +1067,23 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{2964AC08-382B-4FAE-8F45-970C952B4A4E}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{4F4BC68D-37C6-48D9-8A06-4BE787D68532}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
@@ -1049,14 +1093,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1078,7 +1122,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1089,7 +1133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1100,7 +1144,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1111,7 +1155,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" s="4"/>
     </row>
   </sheetData>
@@ -1123,14 +1167,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1141,7 +1185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDBB52A-07B4-4CD4-B2BE-9D76ECEBFC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBCE40D-2811-4562-8E20-1992648835DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -147,7 +147,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,6 +167,12 @@
       <sz val="7"/>
       <color rgb="FF1F1F1F"/>
       <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -191,7 +197,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -201,6 +207,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -576,7 +583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
@@ -643,7 +650,7 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
@@ -660,6 +667,9 @@
       <c r="C7" t="s">
         <v>19</v>
       </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDBB52A-07B4-4CD4-B2BE-9D76ECEBFC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EC0307-D731-4D69-8862-7E6409CF4896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="35">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>Auto</t>
+  </si>
+  <si>
+    <t>FederalProgramCFDA__c</t>
   </si>
 </sst>
 </file>
@@ -576,7 +579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
@@ -644,20 +647,9 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
         <v>19</v>
       </c>
     </row>
@@ -866,7 +858,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
@@ -901,20 +893,9 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
         <v>27</v>
       </c>
     </row>
@@ -986,10 +967,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1035,6 +1016,17 @@
       </c>
       <c r="C4" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5">
+        <v>11.122999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDBB52A-07B4-4CD4-B2BE-9D76ECEBFC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCA97AF-3F55-44F7-A4A4-9BE140726E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -576,7 +576,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
@@ -644,20 +644,9 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
         <v>19</v>
       </c>
     </row>
@@ -672,7 +661,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -739,20 +728,9 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
         <v>27</v>
       </c>
     </row>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCA97AF-3F55-44F7-A4A4-9BE140726E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA021C9-A433-4F2A-8C4F-E26D94BE486D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="35">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -141,13 +141,16 @@
   </si>
   <si>
     <t>Auto</t>
+  </si>
+  <si>
+    <t>FederalProgramCFDA__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,6 +170,12 @@
       <sz val="7"/>
       <color rgb="FF1F1F1F"/>
       <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -191,7 +200,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -201,6 +210,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -483,13 +495,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="51.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,7 +512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -511,7 +523,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -522,7 +534,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -533,7 +545,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -544,7 +556,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -555,7 +567,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -577,14 +589,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -595,7 +607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -606,7 +618,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -617,7 +629,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -628,7 +640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -639,7 +651,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -662,13 +674,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -679,7 +691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -690,7 +702,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -701,7 +713,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -712,7 +724,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -723,7 +735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -745,13 +757,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -762,7 +774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -773,7 +785,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -784,7 +796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -795,7 +807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -806,7 +818,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -817,7 +829,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -828,7 +840,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -845,14 +857,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -863,7 +875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -874,7 +886,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -885,7 +897,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -904,13 +916,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -918,7 +930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -926,7 +938,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -934,7 +946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -942,17 +954,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -964,14 +976,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -982,7 +994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -993,7 +1005,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1004,7 +1016,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1013,6 +1025,17 @@
       </c>
       <c r="C4" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5">
+        <v>11.122999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1027,14 +1050,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1045,7 +1068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1056,7 +1079,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1067,7 +1090,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1078,7 +1101,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1089,7 +1112,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="B6" s="4"/>
     </row>
   </sheetData>
@@ -1101,14 +1124,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1119,7 +1142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>11</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA021C9-A433-4F2A-8C4F-E26D94BE486D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20455FD3-FED2-466D-8CAE-3351C0BF0D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -141,16 +141,13 @@
   </si>
   <si>
     <t>Auto</t>
-  </si>
-  <si>
-    <t>FederalProgramCFDA__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,12 +167,6 @@
       <sz val="7"/>
       <color rgb="FF1F1F1F"/>
       <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="9.8000000000000007"/>
-      <color rgb="FF297BDE"/>
-      <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -200,7 +191,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -210,9 +201,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -495,13 +483,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="51.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -512,7 +500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -523,7 +511,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -534,7 +522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -545,7 +533,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -556,7 +544,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -567,7 +555,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -589,14 +577,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -607,7 +595,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -618,7 +606,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -629,7 +617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -640,7 +628,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -651,7 +639,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -674,13 +662,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -691,7 +679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -702,7 +690,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -713,7 +701,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -724,7 +712,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -735,7 +723,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -757,13 +745,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,7 +762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -785,7 +773,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -796,7 +784,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -807,7 +795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -818,7 +806,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -829,7 +817,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -840,7 +828,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -857,14 +845,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -875,7 +863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -886,7 +874,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -897,7 +885,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -916,13 +904,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -930,7 +918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -938,7 +926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -946,7 +934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -954,17 +942,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -976,14 +964,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.33203125" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -994,7 +982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1005,7 +993,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1016,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1025,17 +1013,6 @@
       </c>
       <c r="C4" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5">
-        <v>11.122999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1050,14 +1027,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1068,7 +1045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1079,7 +1056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1090,7 +1067,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1101,7 +1078,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1112,7 +1089,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="4"/>
     </row>
   </sheetData>
@@ -1124,14 +1101,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1142,7 +1119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EC0307-D731-4D69-8862-7E6409CF4896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E0400C-4FDA-4DA9-9174-9CC0B5DB696D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -141,9 +141,6 @@
   </si>
   <si>
     <t>Auto</t>
-  </si>
-  <si>
-    <t>FederalProgramCFDA__c</t>
   </si>
 </sst>
 </file>
@@ -967,7 +964,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
@@ -1016,17 +1013,6 @@
       </c>
       <c r="C4" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5">
-        <v>11.122999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBCE40D-2811-4562-8E20-1992648835DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E660CC-78E6-4761-A124-F99144205E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -17,6 +17,8 @@
     <sheet name="Edition" sheetId="4" r:id="rId7"/>
     <sheet name="NGOCreation" sheetId="8" r:id="rId8"/>
     <sheet name="NGOEdit" sheetId="9" r:id="rId9"/>
+    <sheet name="Grantee_nonFed" sheetId="12" r:id="rId10"/>
+    <sheet name="Grantee_nonFed_Edition" sheetId="13" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="65">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -141,6 +143,99 @@
   </si>
   <si>
     <t>Auto</t>
+  </si>
+  <si>
+    <t>Automation Runtime Non Federal Program</t>
+  </si>
+  <si>
+    <t>IntermediateAccount__c</t>
+  </si>
+  <si>
+    <t>external</t>
+  </si>
+  <si>
+    <t>FederalProgramCFDA__c</t>
+  </si>
+  <si>
+    <t>Automation test</t>
+  </si>
+  <si>
+    <t>AssistanceType__c</t>
+  </si>
+  <si>
+    <t>UsesAndUseRestrictions__c</t>
+  </si>
+  <si>
+    <t>CredentialsDocumentation__c</t>
+  </si>
+  <si>
+    <t>ApplicantEligibility__c</t>
+  </si>
+  <si>
+    <t>BeneficiaryEligibility__c</t>
+  </si>
+  <si>
+    <t>PreapplicationCoordination__c</t>
+  </si>
+  <si>
+    <t>ApplicationProcedures__c</t>
+  </si>
+  <si>
+    <t>AwardProcedure__c</t>
+  </si>
+  <si>
+    <t>Deadlines__c</t>
+  </si>
+  <si>
+    <t>RangeofApprovalDisApprovalTime__c</t>
+  </si>
+  <si>
+    <t>Appeals__c</t>
+  </si>
+  <si>
+    <t>Renewals__c</t>
+  </si>
+  <si>
+    <t>CriteriaforSelectingProposals__c</t>
+  </si>
+  <si>
+    <t>FormulaandMatchingRequirements__c</t>
+  </si>
+  <si>
+    <t>LengthandTimePhasingofAssistance__c</t>
+  </si>
+  <si>
+    <t>Reports__c</t>
+  </si>
+  <si>
+    <t>Audits__c</t>
+  </si>
+  <si>
+    <t>Records__c</t>
+  </si>
+  <si>
+    <t>RegulationsGuidelinesAndLiterature__c</t>
+  </si>
+  <si>
+    <t>AccountIdentification__c</t>
+  </si>
+  <si>
+    <t>Obligations__c</t>
+  </si>
+  <si>
+    <t>RangeandAverageofFinancialAssistanc__c</t>
+  </si>
+  <si>
+    <t>ProgramAccomplishments__c</t>
+  </si>
+  <si>
+    <t>RegionalOrLocalOffice__c</t>
+  </si>
+  <si>
+    <t>HeadquartersOffice__c</t>
+  </si>
+  <si>
+    <t>www.automation.com</t>
   </si>
 </sst>
 </file>
@@ -197,7 +292,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -208,6 +303,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -581,6 +679,408 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C31BE40D-23CA-4476-8DBE-49FDFAE7A7CD}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9389269E-34D2-4173-BB25-7965191FE6B2}">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C9"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E0400C-4FDA-4DA9-9174-9CC0B5DB696D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EF2726-C402-4A79-9FC5-B4578EAD4327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -661,7 +661,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -728,20 +728,9 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
         <v>27</v>
       </c>
     </row>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E660CC-78E6-4761-A124-F99144205E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC68236-3DC7-495A-B4D7-3ECB4AABA843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
     <sheet name="Creation" sheetId="3" r:id="rId2"/>
-    <sheet name="Creation2" sheetId="10" r:id="rId3"/>
-    <sheet name="Creation1" sheetId="6" r:id="rId4"/>
-    <sheet name="Edition1" sheetId="7" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId6"/>
-    <sheet name="Edition" sheetId="4" r:id="rId7"/>
-    <sheet name="NGOCreation" sheetId="8" r:id="rId8"/>
-    <sheet name="NGOEdit" sheetId="9" r:id="rId9"/>
-    <sheet name="Grantee_nonFed" sheetId="12" r:id="rId10"/>
-    <sheet name="Grantee_nonFed_Edition" sheetId="13" r:id="rId11"/>
+    <sheet name="xss_creation" sheetId="14" r:id="rId3"/>
+    <sheet name="Creation2" sheetId="10" r:id="rId4"/>
+    <sheet name="Creation1" sheetId="6" r:id="rId5"/>
+    <sheet name="Edition1" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId7"/>
+    <sheet name="Edition" sheetId="4" r:id="rId8"/>
+    <sheet name="xss_edition" sheetId="15" r:id="rId9"/>
+    <sheet name="NGOCreation" sheetId="8" r:id="rId10"/>
+    <sheet name="NGOEdit" sheetId="9" r:id="rId11"/>
+    <sheet name="Grantee_nonFed" sheetId="12" r:id="rId12"/>
+    <sheet name="Grantee_nonFed_Edition" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="68">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -236,13 +238,22 @@
   </si>
   <si>
     <t>www.automation.com</t>
+  </si>
+  <si>
+    <t>&lt;xss oncontextmenu="alert(1)" style=display:block&gt;test&lt;/xss&gt;</t>
+  </si>
+  <si>
+    <t>&lt;style&gt;:target {color:red;}&lt;/style&gt;&lt;xss id=x style="transition:color 1s" onwebkittransitionend=alert(1)&gt;&lt;/xss&gt;</t>
+  </si>
+  <si>
+    <t>&lt;marquee width=1 loop=1 onbounce=alert(1)&gt;XSS&lt;/marquee&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,6 +281,13 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -279,7 +297,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -287,12 +305,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -306,6 +339,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -680,6 +725,117 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C31BE40D-23CA-4476-8DBE-49FDFAE7A7CD}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -748,7 +904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9389269E-34D2-4173-BB25-7965191FE6B2}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1181,6 +1337,100 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2D652A-D99B-441E-840C-6B4AD06284BE}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{009DDA18-BD8D-4303-8828-A10C079E0E74}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1274,7 +1524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1374,7 +1624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1433,7 +1683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1494,7 +1744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1556,14 +1806,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
-  <dimension ref="A1:C6"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F71CA3D-11E1-4560-B7C5-60FF3AD25D27}">
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="92.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1577,92 +1827,92 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
+      <c r="C2" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="9"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C8" s="10"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C9" s="12"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C10" s="9"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="C11" s="10"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="9"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="10"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="9"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{18934687-9B8A-408B-A355-2CDC4369A865}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EF2726-C402-4A79-9FC5-B4578EAD4327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464FCCB1-AEB2-47B5-84E4-092909D6A1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
     <sheet name="Creation" sheetId="3" r:id="rId2"/>
-    <sheet name="Creation2" sheetId="10" r:id="rId3"/>
-    <sheet name="Creation1" sheetId="6" r:id="rId4"/>
-    <sheet name="Edition1" sheetId="7" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId6"/>
-    <sheet name="Edition" sheetId="4" r:id="rId7"/>
-    <sheet name="NGOCreation" sheetId="8" r:id="rId8"/>
-    <sheet name="NGOEdit" sheetId="9" r:id="rId9"/>
+    <sheet name="CSS_Creation1" sheetId="12" r:id="rId3"/>
+    <sheet name="CSS_Edition" sheetId="13" r:id="rId4"/>
+    <sheet name="Creation2" sheetId="10" r:id="rId5"/>
+    <sheet name="Creation1" sheetId="6" r:id="rId6"/>
+    <sheet name="Edition1" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId8"/>
+    <sheet name="Edition" sheetId="4" r:id="rId9"/>
+    <sheet name="NGOCreation" sheetId="8" r:id="rId10"/>
+    <sheet name="NGOEdit" sheetId="9" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="70">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -141,13 +143,121 @@
   </si>
   <si>
     <t>Auto</t>
+  </si>
+  <si>
+    <t>&lt;xss onclick="alert(1)" style=display:block&gt;test&lt;/xss&gt;</t>
+  </si>
+  <si>
+    <t>&lt;xss oncontextmenu="alert(1)" style=display:block&gt;test&lt;/xss&gt;</t>
+  </si>
+  <si>
+    <t>Save and Continue</t>
+  </si>
+  <si>
+    <t>Planning</t>
+  </si>
+  <si>
+    <t>Programs</t>
+  </si>
+  <si>
+    <t>Internal Programs</t>
+  </si>
+  <si>
+    <t>Setup</t>
+  </si>
+  <si>
+    <t>ProgramChecklists</t>
+  </si>
+  <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>Responsibilities</t>
+  </si>
+  <si>
+    <t>ProgramReviewerEnhancedGrid</t>
+  </si>
+  <si>
+    <t>Responsibility__c</t>
+  </si>
+  <si>
+    <t>Files</t>
+  </si>
+  <si>
+    <t>InternalProgramContentNotes</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>ModalLayout</t>
+  </si>
+  <si>
+    <t>PageLayout</t>
+  </si>
+  <si>
+    <t>Save</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>Navigator</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Add</t>
+  </si>
+  <si>
+    <t>name__r.name</t>
+  </si>
+  <si>
+    <t>Automation PM</t>
+  </si>
+  <si>
+    <t>ReviewerRole__c</t>
+  </si>
+  <si>
+    <t>Program Reviewer</t>
+  </si>
+  <si>
+    <t>DueDate__c</t>
+  </si>
+  <si>
+    <t>AllowRecordEdit__c</t>
+  </si>
+  <si>
+    <t>Objectives__c1</t>
+  </si>
+  <si>
+    <t>test1</t>
+  </si>
+  <si>
+    <t>Edit</t>
+  </si>
+  <si>
+    <t>&lt;body onload=alert(5000)&gt;</t>
+  </si>
+  <si>
+    <t>FederalProgramCFDA__c11.233</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,6 +277,24 @@
       <sz val="7"/>
       <color rgb="FF1F1F1F"/>
       <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -191,7 +319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -201,6 +329,11 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -483,13 +616,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="51.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,7 +633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -511,7 +644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -522,7 +655,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -533,7 +666,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -544,7 +677,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -555,7 +688,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -574,17 +707,128 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -595,7 +839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -606,7 +850,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -617,7 +861,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -628,7 +872,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -639,7 +883,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -649,6 +893,12 @@
       <c r="C6" t="s">
         <v>19</v>
       </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" s="1"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="C10" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -660,15 +910,940 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF1A7D3-1D83-420A-85C3-335ABA9E41FD}">
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" customWidth="1"/>
+    <col min="3" max="3" width="45.33203125" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C61" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{463F601C-E8CE-4475-B667-B160977BBA14}"/>
+    <hyperlink ref="C45" r:id="rId2" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{9AFFC7AD-4DC4-4AFF-A13D-1402AF5E6E23}"/>
+    <hyperlink ref="C52" r:id="rId3" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{A0670C0D-B9B4-4992-B59E-E30E38E13116}"/>
+    <hyperlink ref="C59" r:id="rId4" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{26C1BDB4-8376-4BC7-A663-C3507E44397E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3A50D7-EDBA-423C-B25B-4864DAF5BE8D}">
+  <dimension ref="A1:D52"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="3" max="3" width="45.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -679,7 +1854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -690,7 +1865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -701,7 +1876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -712,7 +1887,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -723,7 +1898,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -742,16 +1917,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -762,7 +1937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -773,7 +1948,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -784,7 +1959,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -795,7 +1970,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -806,7 +1981,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -817,7 +1992,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -828,7 +2003,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -842,17 +2017,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -863,7 +2038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -874,7 +2049,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -890,16 +2065,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -907,7 +2082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -915,7 +2090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -923,7 +2098,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -931,17 +2106,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -951,16 +2126,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -971,7 +2146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -982,7 +2157,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -993,7 +2168,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1011,115 +2186,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBCE40D-2811-4562-8E20-1992648835DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCAB530-C222-443E-BB4D-0D5C3678D8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464FCCB1-AEB2-47B5-84E4-092909D6A1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DABA2D6F-F269-4FBB-B943-201AF573243D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="70">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -615,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -682,20 +682,9 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
         <v>19</v>
       </c>
     </row>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDBB52A-07B4-4CD4-B2BE-9D76ECEBFC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFCAA56-33CA-46AA-8314-5944D7D439D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
     <sheet name="Creation" sheetId="3" r:id="rId2"/>
-    <sheet name="Creation2" sheetId="10" r:id="rId3"/>
-    <sheet name="Creation1" sheetId="6" r:id="rId4"/>
-    <sheet name="Edition1" sheetId="7" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId6"/>
-    <sheet name="Edition" sheetId="4" r:id="rId7"/>
-    <sheet name="NGOCreation" sheetId="8" r:id="rId8"/>
-    <sheet name="NGOEdit" sheetId="9" r:id="rId9"/>
+    <sheet name="Creation_new" sheetId="12" r:id="rId3"/>
+    <sheet name="Creation2" sheetId="10" r:id="rId4"/>
+    <sheet name="Creation1" sheetId="6" r:id="rId5"/>
+    <sheet name="Edition1" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId7"/>
+    <sheet name="Edition" sheetId="4" r:id="rId8"/>
+    <sheet name="NGOCreation" sheetId="8" r:id="rId9"/>
+    <sheet name="NGOEdit" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="53">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -141,6 +142,63 @@
   </si>
   <si>
     <t>Auto</t>
+  </si>
+  <si>
+    <t>ModalButton</t>
+  </si>
+  <si>
+    <t>Save and Continue</t>
+  </si>
+  <si>
+    <t>TabClick</t>
+  </si>
+  <si>
+    <t>Responsibilities</t>
+  </si>
+  <si>
+    <t>TableAction</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>TableData</t>
+  </si>
+  <si>
+    <t>ProgramRolesAndResponsibilitiesInternalProg</t>
+  </si>
+  <si>
+    <t>Automation PM</t>
+  </si>
+  <si>
+    <t>Field Value1</t>
+  </si>
+  <si>
+    <t>name__r.name</t>
+  </si>
+  <si>
+    <t>AnnouncementRole__c</t>
+  </si>
+  <si>
+    <t>Step 1</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Save</t>
+  </si>
+  <si>
+    <t>Assertion</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Published</t>
+  </si>
+  <si>
+    <t>softly see</t>
   </si>
 </sst>
 </file>
@@ -483,13 +541,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,7 +558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -511,7 +569,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -522,7 +580,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -533,7 +591,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -544,7 +602,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -555,7 +613,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -574,17 +632,54 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -595,7 +690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -606,7 +701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -617,7 +712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -628,7 +723,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -639,7 +734,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -650,7 +745,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -671,15 +766,273 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB2CDC6-FDA7-4555-AB20-1050659065EB}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" customWidth="1"/>
+    <col min="5" max="5" width="39.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{546BDCBE-90FF-419A-8DC1-D7E2F301FD40}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,7 +1043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -701,7 +1054,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -712,7 +1065,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -723,7 +1076,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -734,7 +1087,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -745,7 +1098,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -764,16 +1117,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -784,7 +1137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -795,7 +1148,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -806,7 +1159,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -817,7 +1170,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -828,7 +1181,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -839,7 +1192,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -850,7 +1203,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -864,17 +1217,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -885,7 +1238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -896,7 +1249,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -907,7 +1260,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -916,67 +1269,6 @@
       </c>
       <c r="C4" t="s">
         <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -985,15 +1277,76 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1004,7 +1357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1015,7 +1368,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1026,7 +1379,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1046,17 +1399,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1078,7 +1431,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1089,7 +1442,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1100,7 +1453,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1111,48 +1464,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC68236-3DC7-495A-B4D7-3ECB4AABA843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD217C3-9947-46C8-AC41-75BF9BD7539E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3384" yWindow="1164" windowWidth="17280" windowHeight="8880" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -325,7 +325,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -345,11 +345,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -901,6 +899,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1876,37 +1875,21 @@
       <c r="B7" s="7"/>
       <c r="C7" s="9"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C8" s="10"/>
-    </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C9" s="12"/>
+      <c r="C9" s="10"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C10" s="9"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="C11" s="10"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="9"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="10"/>
-    </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
+      <c r="C14" s="10"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
       <c r="C15" s="9"/>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,22 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464FCCB1-AEB2-47B5-84E4-092909D6A1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F1A84D-233C-4986-902E-01C8866114CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3384" yWindow="1164" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
     <sheet name="Creation" sheetId="3" r:id="rId2"/>
     <sheet name="CSS_Creation1" sheetId="12" r:id="rId3"/>
-    <sheet name="CSS_Edition" sheetId="13" r:id="rId4"/>
-    <sheet name="Creation2" sheetId="10" r:id="rId5"/>
-    <sheet name="Creation1" sheetId="6" r:id="rId6"/>
-    <sheet name="Edition1" sheetId="7" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId8"/>
-    <sheet name="Edition" sheetId="4" r:id="rId9"/>
-    <sheet name="NGOCreation" sheetId="8" r:id="rId10"/>
-    <sheet name="NGOEdit" sheetId="9" r:id="rId11"/>
+    <sheet name="Test_XSS" sheetId="14" r:id="rId4"/>
+    <sheet name="CSS_Edition" sheetId="13" r:id="rId5"/>
+    <sheet name="Creation2" sheetId="10" r:id="rId6"/>
+    <sheet name="Creation1" sheetId="6" r:id="rId7"/>
+    <sheet name="Edition1" sheetId="7" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId9"/>
+    <sheet name="Edition" sheetId="4" r:id="rId10"/>
+    <sheet name="NGOCreation" sheetId="8" r:id="rId11"/>
+    <sheet name="NGOEdit" sheetId="9" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="82">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -226,6 +227,21 @@
     <t>Automation PM</t>
   </si>
   <si>
+    <t>Objectives__c1</t>
+  </si>
+  <si>
+    <t>test1</t>
+  </si>
+  <si>
+    <t>Edit</t>
+  </si>
+  <si>
+    <t>&lt;body onload=alert(5000)&gt;</t>
+  </si>
+  <si>
+    <t>FederalProgramCFDA__c</t>
+  </si>
+  <si>
     <t>ReviewerRole__c</t>
   </si>
   <si>
@@ -238,25 +254,49 @@
     <t>AllowRecordEdit__c</t>
   </si>
   <si>
-    <t>Objectives__c1</t>
-  </si>
-  <si>
-    <t>test1</t>
-  </si>
-  <si>
-    <t>Edit</t>
-  </si>
-  <si>
-    <t>&lt;body onload=alert(5000)&gt;</t>
-  </si>
-  <si>
-    <t>FederalProgramCFDA__c11.233</t>
+    <t>Add Files</t>
+  </si>
+  <si>
+    <t>GrantorInternalProgramFiles</t>
+  </si>
+  <si>
+    <t>Attachment</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Attachment.pdf</t>
+  </si>
+  <si>
+    <t>Internal Programs - All</t>
+  </si>
+  <si>
+    <t>Toggle</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>View</t>
+  </si>
+  <si>
+    <t>Other Artifacts</t>
+  </si>
+  <si>
+    <t>PR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="11"/>
@@ -319,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -334,6 +374,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -708,6 +751,68 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{2964AC08-382B-4FAE-8F45-970C952B4A4E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -781,7 +886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -911,11 +1016,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF1A7D3-1D83-420A-85C3-335ABA9E41FD}">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" customWidth="1"/>
     <col min="3" max="3" width="45.33203125" customWidth="1"/>
     <col min="4" max="4" width="19.109375" customWidth="1"/>
   </cols>
@@ -935,56 +1040,56 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>34</v>
+      <c r="A2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>5</v>
+      <c r="A3" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
+        <v>78</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
@@ -994,11 +1099,11 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -1006,21 +1111,27 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>69</v>
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
@@ -1031,10 +1142,10 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
@@ -1044,11 +1155,11 @@
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" t="s">
-        <v>52</v>
+      <c r="B10" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -1058,11 +1169,11 @@
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>68</v>
+      <c r="B11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="8">
+        <v>11.233000000000001</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
@@ -1070,13 +1181,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
@@ -1084,27 +1195,27 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>41</v>
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
@@ -1112,55 +1223,405 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
         <v>53</v>
       </c>
-      <c r="D15" t="s">
-        <v>55</v>
+      <c r="D19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25">
+        <v>10</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>37</v>
       </c>
       <c r="B41" t="s">
         <v>38</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>39</v>
+      <c r="C41" t="s">
+        <v>34</v>
       </c>
       <c r="D41" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>55</v>
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" t="s">
+        <v>64</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -1171,136 +1632,52 @@
         <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>5</v>
-      </c>
-      <c r="B46" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47" t="s">
-        <v>36</v>
-      </c>
-      <c r="D47" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="1" t="s">
+    <row r="51" spans="1:4">
+      <c r="A51" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B51" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C51" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D51" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" s="1" t="s">
+    <row r="52" spans="1:4">
+      <c r="A52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>5</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D50" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>5</v>
-      </c>
-      <c r="B51" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
-        <v>5</v>
-      </c>
-      <c r="B52" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" t="s">
-        <v>5</v>
+      <c r="D52" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>5</v>
       </c>
-      <c r="B53" t="s">
-        <v>18</v>
-      </c>
-      <c r="C53" t="s">
-        <v>19</v>
+      <c r="B53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
@@ -1310,95 +1687,95 @@
       <c r="A54" t="s">
         <v>5</v>
       </c>
-      <c r="B54" s="6" t="s">
-        <v>51</v>
+      <c r="B54" t="s">
+        <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="1" t="s">
-        <v>37</v>
+      <c r="A55" t="s">
+        <v>5</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>39</v>
+        <v>10</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D55" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>55</v>
+      <c r="A56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>5</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>35</v>
+      <c r="B57" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C57" t="s">
+        <v>36</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" t="s">
-        <v>5</v>
+      <c r="A58" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="B58" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" t="s">
-        <v>8</v>
+        <v>38</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="D58" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" t="s">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>10</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D59" t="s">
-        <v>5</v>
+      <c r="A59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>5</v>
       </c>
-      <c r="B60" t="s">
-        <v>18</v>
-      </c>
-      <c r="C60" t="s">
-        <v>19</v>
+      <c r="B60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
@@ -1408,22 +1785,162 @@
       <c r="A61" t="s">
         <v>5</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C64" t="s">
         <v>36</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D65" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>5</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C71" t="s">
+        <v>36</v>
+      </c>
+      <c r="D71" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{463F601C-E8CE-4475-B667-B160977BBA14}"/>
-    <hyperlink ref="C45" r:id="rId2" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{9AFFC7AD-4DC4-4AFF-A13D-1402AF5E6E23}"/>
-    <hyperlink ref="C52" r:id="rId3" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{A0670C0D-B9B4-4992-B59E-E30E38E13116}"/>
-    <hyperlink ref="C59" r:id="rId4" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{26C1BDB4-8376-4BC7-A663-C3507E44397E}"/>
+    <hyperlink ref="C8" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{463F601C-E8CE-4475-B667-B160977BBA14}"/>
+    <hyperlink ref="C55" r:id="rId2" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{9AFFC7AD-4DC4-4AFF-A13D-1402AF5E6E23}"/>
+    <hyperlink ref="C62" r:id="rId3" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{A0670C0D-B9B4-4992-B59E-E30E38E13116}"/>
+    <hyperlink ref="C69" r:id="rId4" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{26C1BDB4-8376-4BC7-A663-C3507E44397E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
@@ -1431,8 +1948,43 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{586F5ADE-5CD6-4B7B-BF81-FB1528D9AA67}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="33.5546875" customWidth="1"/>
+    <col min="3" max="3" width="51.21875" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:4" customFormat="1"/>
+    <row r="3" spans="1:4" customFormat="1"/>
+    <row r="4" spans="1:4" customFormat="1"/>
+    <row r="5" spans="1:4" customFormat="1">
+      <c r="B5" s="6"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" customFormat="1">
+      <c r="B6" s="6"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" customFormat="1">
+      <c r="B7" s="6"/>
+      <c r="D7" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3A50D7-EDBA-423C-B25B-4864DAF5BE8D}">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
@@ -1456,72 +2008,72 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
+        <v>43</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
+        <v>43</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" t="s">
-        <v>55</v>
+        <v>67</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s">
-        <v>55</v>
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1529,66 +2081,66 @@
         <v>43</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" t="s">
-        <v>55</v>
+        <v>68</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>59</v>
+      <c r="B8" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>45</v>
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
       </c>
       <c r="C9" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>44</v>
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
       </c>
       <c r="C10" t="s">
         <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>47</v>
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
         <v>55</v>
@@ -1596,10 +2148,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
         <v>34</v>
@@ -1610,27 +2162,27 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
         <v>55</v>
@@ -1640,7 +2192,7 @@
       <c r="A15" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C15" t="s">
@@ -1658,7 +2210,7 @@
         <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -1672,7 +2224,7 @@
         <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -1688,30 +2240,33 @@
       <c r="C18" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
+        <v>46</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
@@ -1719,13 +2274,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" t="s">
-        <v>65</v>
+        <v>46</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
@@ -1733,100 +2288,360 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
         <v>11</v>
       </c>
-      <c r="B22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
+      <c r="B54" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55" t="s">
+        <v>53</v>
+      </c>
+      <c r="D55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" t="s">
+        <v>58</v>
+      </c>
+      <c r="D56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" t="s">
+        <v>53</v>
+      </c>
+      <c r="D58" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60">
+        <v>10</v>
+      </c>
+      <c r="D60" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C61" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D63" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C64" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C66" t="s">
+        <v>50</v>
+      </c>
+      <c r="D66" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>46</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C67" t="s">
+        <v>53</v>
+      </c>
+      <c r="D67" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>46</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C68" t="s">
+        <v>57</v>
+      </c>
+      <c r="D68" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>46</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69" t="s">
+        <v>50</v>
+      </c>
+      <c r="D69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>46</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C70" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>46</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C71" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
         <v>11</v>
       </c>
-      <c r="B23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
+      <c r="B72" t="s">
+        <v>52</v>
+      </c>
+      <c r="C72" t="s">
+        <v>63</v>
+      </c>
+      <c r="D72" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
         <v>11</v>
       </c>
-      <c r="B24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="B73" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" t="s">
+        <v>61</v>
+      </c>
+      <c r="C74" t="s">
+        <v>62</v>
+      </c>
+      <c r="D74" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" t="s">
+        <v>61</v>
+      </c>
+      <c r="C75" t="s">
+        <v>62</v>
+      </c>
+      <c r="D75" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" t="s">
+        <v>61</v>
+      </c>
+      <c r="C76" t="s">
+        <v>62</v>
+      </c>
+      <c r="D76" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" t="s">
+        <v>61</v>
+      </c>
+      <c r="C77" t="s">
+        <v>62</v>
+      </c>
+      <c r="D77" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>5</v>
+      </c>
+      <c r="B78" t="s">
         <v>52</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C78" t="s">
         <v>53</v>
-      </c>
-      <c r="D25" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C50" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C52" t="s">
-        <v>27</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1834,7 +2649,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1917,7 +2732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -2017,7 +2832,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -2065,7 +2880,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -2124,66 +2939,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{2964AC08-382B-4FAE-8F45-970C952B4A4E}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
-</worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F1A84D-233C-4986-902E-01C8866114CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129D17C4-DA1F-4E4B-8D62-A29F69A0CC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3384" yWindow="1164" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="83">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>PR</t>
+  </si>
+  <si>
+    <t>Programs111</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1075,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>57</v>
@@ -1962,18 +1965,15 @@
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:4" customFormat="1"/>
-    <row r="3" spans="1:4" customFormat="1"/>
-    <row r="4" spans="1:4" customFormat="1"/>
-    <row r="5" spans="1:4" customFormat="1">
+    <row r="5" spans="1:4">
       <c r="B5" s="6"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" customFormat="1">
+    <row r="6" spans="1:4">
       <c r="B6" s="6"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" customFormat="1">
+    <row r="7" spans="1:4">
       <c r="B7" s="6"/>
       <c r="D7" s="1"/>
     </row>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD217C3-9947-46C8-AC41-75BF9BD7539E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3F2702-97E9-46B5-963D-02A32216B65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3384" yWindow="1164" windowWidth="17280" windowHeight="8880" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="69">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>&lt;marquee width=1 loop=1 onbounce=alert(1)&gt;XSS&lt;/marquee&gt;</t>
+  </si>
+  <si>
+    <t>LA County Parks</t>
   </si>
 </sst>
 </file>
@@ -631,13 +634,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -648,7 +651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -659,7 +662,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -670,7 +673,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -681,7 +684,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -692,7 +695,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -703,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -725,14 +728,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -743,7 +746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -754,7 +757,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -765,7 +768,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -776,7 +779,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -787,7 +790,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
     </row>
   </sheetData>
@@ -799,14 +802,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -817,7 +820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -836,13 +839,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C31BE40D-23CA-4476-8DBE-49FDFAE7A7CD}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -853,7 +856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -864,7 +867,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -875,7 +878,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -886,7 +889,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -906,13 +909,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9389269E-34D2-4173-BB25-7965191FE6B2}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -923,7 +926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -934,7 +937,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -945,7 +948,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -956,7 +959,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -967,7 +970,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -978,7 +981,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -989,7 +992,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1000,7 +1003,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1011,7 +1014,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1022,7 +1025,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1033,7 +1036,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1044,7 +1047,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1055,7 +1058,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -1066,7 +1069,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1077,7 +1080,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -1088,7 +1091,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -1099,7 +1102,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -1110,7 +1113,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1121,7 +1124,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -1132,7 +1135,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -1143,7 +1146,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -1154,7 +1157,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -1165,7 +1168,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -1176,7 +1179,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -1187,7 +1190,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -1198,7 +1201,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1209,7 +1212,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -1220,7 +1223,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -1239,14 +1242,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1257,7 +1260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1268,7 +1271,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1279,7 +1282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1287,10 +1290,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1301,7 +1304,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1312,7 +1315,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1323,7 +1326,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="5"/>
     </row>
   </sheetData>
@@ -1338,13 +1341,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2D652A-D99B-441E-840C-6B4AD06284BE}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1355,7 +1358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1366,7 +1369,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1377,7 +1380,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1388,7 +1391,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1399,7 +1402,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1410,7 +1413,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1432,13 +1435,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1449,7 +1452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1460,7 +1463,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1471,7 +1474,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1482,7 +1485,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1493,7 +1496,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1504,7 +1507,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1526,13 +1529,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1543,7 +1546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1554,7 +1557,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1565,7 +1568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1576,7 +1579,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1587,7 +1590,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1598,7 +1601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1609,7 +1612,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1626,14 +1629,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1644,7 +1647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1655,7 +1658,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1666,7 +1669,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1685,13 +1688,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1699,7 +1702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1707,7 +1710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1715,7 +1718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1723,17 +1726,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1746,13 +1749,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1763,7 +1766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1774,7 +1777,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1785,7 +1788,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1808,14 +1811,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F71CA3D-11E1-4560-B7C5-60FF3AD25D27}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="92.77734375" customWidth="1"/>
+    <col min="3" max="3" width="92.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1826,7 +1829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
@@ -1837,7 +1840,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1848,7 +1851,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1859,7 +1862,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1870,26 +1873,26 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="9"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" s="10"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C10" s="9"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="9"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C14" s="10"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C15" s="9"/>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD217C3-9947-46C8-AC41-75BF9BD7539E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3384" yWindow="1164" windowWidth="17280" windowHeight="8880" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -631,13 +631,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -648,7 +648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -659,7 +659,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -670,7 +670,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -681,7 +681,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -692,7 +692,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -703,7 +703,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -725,14 +725,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -754,7 +754,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -765,7 +765,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -776,7 +776,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -787,7 +787,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" s="4"/>
     </row>
   </sheetData>
@@ -799,14 +799,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -817,7 +817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -836,13 +836,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C31BE40D-23CA-4476-8DBE-49FDFAE7A7CD}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -853,7 +853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -864,7 +864,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -875,7 +875,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -886,7 +886,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -906,13 +906,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9389269E-34D2-4173-BB25-7965191FE6B2}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -923,7 +923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -934,7 +934,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -945,7 +945,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -956,7 +956,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -967,7 +967,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -978,7 +978,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -989,7 +989,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -1239,14 +1239,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" s="5"/>
     </row>
   </sheetData>
@@ -1338,13 +1338,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2D652A-D99B-441E-840C-6B4AD06284BE}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1432,13 +1432,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1526,13 +1526,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1626,14 +1626,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1685,13 +1685,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1723,17 +1723,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1746,13 +1746,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1808,14 +1808,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F71CA3D-11E1-4560-B7C5-60FF3AD25D27}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="92.77734375" customWidth="1"/>
+    <col min="3" max="3" width="92.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1870,26 +1870,26 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="9"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C9" s="10"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C10" s="9"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="9"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C14" s="10"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C15" s="9"/>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD217C3-9947-46C8-AC41-75BF9BD7539E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B69143-4346-448D-B862-63548E1446BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1261,7 +1261,7 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
@@ -1305,7 +1305,7 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B69143-4346-448D-B862-63548E1446BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F32CBC7-3D94-4F94-A8A8-E5052F7DC704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1238,7 +1238,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.90625" bestFit="1" customWidth="1"/>
@@ -1284,10 +1284,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1295,7 +1295,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -1306,7 +1306,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -1317,18 +1317,18 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B9" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B8" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{7EE9E90B-967F-44F2-8381-163CD7361D89}"/>
+    <hyperlink ref="C7" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{7EE9E90B-967F-44F2-8381-163CD7361D89}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
